--- a/FORMATO PARA 1.º y 2.º BGU.xlsx
+++ b/FORMATO PARA 1.º y 2.º BGU.xlsx
@@ -3,19 +3,32 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33A63DE1-38D2-4B40-8D98-C568439E048D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94A0A0E2-655B-4BFE-BE86-22C5E543D827}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Reporte Periodo" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="71">
   <si>
     <t>UNIDAD EDUCATIVA EMILIANO HINOSTROZA</t>
   </si>
@@ -26,42 +39,18 @@
     <t>FÍSICA</t>
   </si>
   <si>
-    <t>MATEMÁTICA SUPERIOR</t>
-  </si>
-  <si>
-    <t>SOCIOLOGÍA</t>
-  </si>
-  <si>
     <t>MATEMÁTICA</t>
   </si>
   <si>
-    <t>REDACCIÓN CREATIVA</t>
-  </si>
-  <si>
     <t>LENGUA Y LITERATURA</t>
   </si>
   <si>
-    <t xml:space="preserve">BIOLOGÍA </t>
-  </si>
-  <si>
     <t>QUÍMICA</t>
   </si>
   <si>
-    <t>QUÍMICA SUPERIOR</t>
-  </si>
-  <si>
-    <t>INVESTIGACIÓN EN CIENCIA Y TECNOLOGÍA</t>
-  </si>
-  <si>
-    <t>CÍVICA Y ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
-  </si>
-  <si>
     <t>HISTORIA</t>
   </si>
   <si>
-    <t xml:space="preserve">EMPRENDIMIENTO Y GESTIÓN </t>
-  </si>
-  <si>
     <t>INGLÉS</t>
   </si>
   <si>
@@ -236,7 +225,22 @@
     <t xml:space="preserve">EDUCACION INICIAL </t>
   </si>
   <si>
-    <t>EVALUACIÓN COMPORTAMENTAL</t>
+    <t>BIOLOGÍA</t>
+  </si>
+  <si>
+    <t>EDUCACIÓN PARA LA CIUDADANÍA</t>
+  </si>
+  <si>
+    <t>FILOSOFÍA</t>
+  </si>
+  <si>
+    <t>EDUCACIÓN CULTURAL Y ARTÍSTICA</t>
+  </si>
+  <si>
+    <t>EMPRENDIMIENTO Y GESTIÓN</t>
+  </si>
+  <si>
+    <t>ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
   </si>
 </sst>
 </file>
@@ -685,7 +689,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF18"/>
+  <dimension ref="A1:AE18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.21875" customWidth="1"/>
@@ -694,17 +698,20 @@
     <col min="4" max="4" width="34.33203125" customWidth="1"/>
     <col min="5" max="12" width="30" customWidth="1"/>
     <col min="13" max="13" width="49.88671875" customWidth="1"/>
-    <col min="14" max="17" width="30" customWidth="1"/>
-    <col min="18" max="18" width="34.109375" customWidth="1"/>
-    <col min="27" max="27" width="0" hidden="1" customWidth="1"/>
-    <col min="28" max="28" width="39.21875" hidden="1" customWidth="1"/>
-    <col min="29" max="29" width="33.21875" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="30" customWidth="1"/>
+    <col min="15" max="15" width="48.109375" customWidth="1"/>
+    <col min="24" max="24" width="0" hidden="1" customWidth="1"/>
+    <col min="25" max="25" width="39.21875" hidden="1" customWidth="1"/>
+    <col min="26" max="26" width="33.21875" hidden="1" customWidth="1"/>
+    <col min="27" max="27" width="15.109375" hidden="1" customWidth="1"/>
+    <col min="28" max="28" width="29.44140625" hidden="1" customWidth="1"/>
+    <col min="29" max="29" width="0" hidden="1" customWidth="1"/>
     <col min="30" max="30" width="15.109375" hidden="1" customWidth="1"/>
     <col min="31" max="31" width="29.44140625" hidden="1" customWidth="1"/>
-    <col min="32" max="37" width="0" hidden="1" customWidth="1"/>
+    <col min="32" max="34" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="19.8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:29" ht="19.8" x14ac:dyDescent="0.4">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -718,220 +725,211 @@
       <c r="I1" s="8"/>
       <c r="J1" s="8"/>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC4" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C2" s="5" t="s">
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="B5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="B6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>66</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>34</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC5" t="s">
+      <c r="B7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z7" t="s">
         <v>39</v>
       </c>
-      <c r="AD5" t="s">
+      <c r="AA7" t="s">
         <v>40</v>
       </c>
-      <c r="AE5" t="s">
-        <v>41</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>69</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>70</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
-      <c r="AB8" t="s">
-        <v>71</v>
-      </c>
-      <c r="AC8" t="s">
-        <v>49</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="Y8" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="E9" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H9" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="L9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="N9" s="2" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC9" t="s">
-        <v>51</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="4"/>
       <c r="C10" s="3"/>
@@ -947,17 +945,14 @@
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-      <c r="AC10" t="s">
+      <c r="Z10" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA10" t="s">
         <v>53</v>
       </c>
-      <c r="AD10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
       <c r="B11" s="4"/>
       <c r="C11" s="3"/>
@@ -973,17 +968,14 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-      <c r="AC11" t="s">
+      <c r="Z11" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA11" t="s">
         <v>54</v>
       </c>
-      <c r="AD11" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A12" s="7"/>
       <c r="B12" s="4"/>
       <c r="C12" s="3"/>
@@ -999,17 +991,14 @@
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
-      <c r="AC12" t="s">
+      <c r="Z12" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA12" t="s">
         <v>55</v>
       </c>
-      <c r="AD12" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A13" s="7"/>
       <c r="B13" s="4"/>
       <c r="C13" s="3"/>
@@ -1025,17 +1014,14 @@
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-      <c r="AC13" t="s">
+      <c r="Z13" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA13" t="s">
         <v>56</v>
       </c>
-      <c r="AD13" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A14" s="7"/>
       <c r="B14" s="4"/>
       <c r="C14" s="3"/>
@@ -1051,17 +1037,14 @@
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
-      <c r="P14" s="3"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
-      <c r="AC14" t="s">
+      <c r="Z14" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA14" t="s">
         <v>57</v>
       </c>
-      <c r="AD14" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A15" s="7"/>
       <c r="B15" s="4"/>
       <c r="C15" s="3"/>
@@ -1077,14 +1060,11 @@
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="3"/>
-      <c r="AC15" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="Z15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A16" s="7"/>
       <c r="B16" s="4"/>
       <c r="C16" s="3"/>
@@ -1100,21 +1080,18 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
-      <c r="AC16" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC17" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC18" t="s">
-        <v>22</v>
+      <c r="Z16" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="26:26" x14ac:dyDescent="0.3">
+      <c r="Z17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="26:26" x14ac:dyDescent="0.3">
+      <c r="Z18" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1123,19 +1100,19 @@
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{BA29F8F6-4357-424C-926B-ABF848246A12}">
-      <formula1>$AB$4:AB$9</formula1>
+      <formula1>$Y$4:Y$9</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3" xr:uid="{1111DBC0-3B92-4B3D-A296-AB24C7349FBB}">
-      <formula1>$AC$4:$AC$18</formula1>
+      <formula1>$Z$4:$Z$18</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4" xr:uid="{08909813-B489-4B84-A754-485066F9D523}">
-      <formula1>AE$4:AE$6</formula1>
+      <formula1>AB$4:AB$6</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5" xr:uid="{D0130D7C-E58C-49AD-B5F3-99115349199D}">
-      <formula1>$AD$4:$AD$14</formula1>
+      <formula1>$AA$4:$AA$14</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B6" xr:uid="{D03738F8-5189-4E2B-948E-C83D3DB07424}">
-      <formula1>$AF$4:$AF$6</formula1>
+      <formula1>$AC$4:$AC$6</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/FORMATO PARA 1.º y 2.º BGU.xlsx
+++ b/FORMATO PARA 1.º y 2.º BGU.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94A0A0E2-655B-4BFE-BE86-22C5E543D827}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94EF147E-0430-4696-9EAB-0396063568F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="72">
   <si>
     <t>UNIDAD EDUCATIVA EMILIANO HINOSTROZA</t>
   </si>
@@ -241,6 +241,9 @@
   </si>
   <si>
     <t>ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
+  </si>
+  <si>
+    <t>EVALUACIÓN COMPORTAMENTAL</t>
   </si>
 </sst>
 </file>
@@ -700,6 +703,7 @@
     <col min="13" max="13" width="49.88671875" customWidth="1"/>
     <col min="14" max="14" width="30" customWidth="1"/>
     <col min="15" max="15" width="48.109375" customWidth="1"/>
+    <col min="16" max="16" width="37" customWidth="1"/>
     <col min="24" max="24" width="0" hidden="1" customWidth="1"/>
     <col min="25" max="25" width="39.21875" hidden="1" customWidth="1"/>
     <col min="26" max="26" width="33.21875" hidden="1" customWidth="1"/>
@@ -918,6 +922,9 @@
       </c>
       <c r="O9" s="2" t="s">
         <v>70</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="Y9" t="s">
         <v>64</v>
@@ -945,6 +952,7 @@
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
       <c r="Z10" t="s">
         <v>45</v>
       </c>
@@ -968,6 +976,7 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
       <c r="Z11" t="s">
         <v>46</v>
       </c>
@@ -991,6 +1000,7 @@
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
       <c r="Z12" t="s">
         <v>47</v>
       </c>
@@ -1014,6 +1024,7 @@
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
       <c r="Z13" t="s">
         <v>48</v>
       </c>
@@ -1037,6 +1048,7 @@
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
+      <c r="P14" s="3"/>
       <c r="Z14" t="s">
         <v>49</v>
       </c>
@@ -1060,6 +1072,7 @@
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
+      <c r="P15" s="3"/>
       <c r="Z15" t="s">
         <v>50</v>
       </c>
@@ -1080,6 +1093,7 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
       <c r="Z16" t="s">
         <v>51</v>
       </c>
